--- a/outputs/daily/hr_rankings_2026-10-26_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-26_remaining.xlsx
@@ -760,12 +760,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>55.7</v>
+        <v>57.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>38.7</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1036,12 +1040,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52.7</v>
+        <v>55.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>33.4</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1287,24 +1295,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -1312,31 +1320,31 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.9</v>
+        <v>51.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,62 +1358,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>48.9</v>
+        <v>50.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>28.9</v>
+        <v>63.3</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1425,12 +1429,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1440,12 +1444,12 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1455,101 +1459,109 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1563,24 +1575,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -1588,31 +1600,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.8</v>
+        <v>50.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,62 +1638,58 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>50.1</v>
+        <v>43.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>33.4</v>
+        <v>38.7</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>63.3</v>
+        <v>0</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1701,27 +1709,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1731,101 +1739,109 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1839,24 +1855,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -1864,31 +1880,31 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>48.1</v>
+        <v>49.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,62 +1918,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.6</v>
+        <v>41</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.4</v>
+        <v>38.7</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>65.2</v>
+        <v>20.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1977,27 +1989,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2007,101 +2019,109 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2115,24 +2135,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -2140,31 +2160,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.4</v>
+        <v>48.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,62 +2198,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>65.2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2253,27 +2269,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2283,101 +2299,109 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2391,24 +2415,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -2416,31 +2440,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>47.4</v>
+        <v>48.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,62 +2478,58 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>38.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2529,27 +2549,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2559,101 +2579,109 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2692,12 +2720,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2716,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>47</v>
+        <v>48.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2740,10 +2768,10 @@
         <v>33.4</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
@@ -2753,39 +2781,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2928,8 +2952,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2968,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2992,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.2</v>
+        <v>46.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3048,10 @@
         <v>33.4</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -3029,39 +3061,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3204,8 +3232,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3219,24 +3255,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -3244,31 +3280,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.3</v>
+        <v>45.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,62 +3318,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>38.2</v>
+        <v>43.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>33.4</v>
+        <v>38.7</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>25.3</v>
+        <v>54.9</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3357,12 +3389,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3372,12 +3404,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3387,101 +3419,109 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3520,12 +3560,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3544,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,7 +3598,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3568,10 +3608,10 @@
         <v>38.7</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T12" t="n">
         <v>78</v>
@@ -3581,39 +3621,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3756,8 +3792,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3771,12 +3815,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3796,12 +3840,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3820,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.9</v>
+        <v>38.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,62 +3878,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>23.3</v>
+        <v>11.6</v>
       </c>
       <c r="Q13" t="n">
         <v>38.7</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3914,7 +3954,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3924,7 +3964,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -3939,67 +3979,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -4032,8 +4072,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4072,12 +4120,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4096,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>34</v>
+        <v>34.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,7 +4158,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4120,10 +4168,10 @@
         <v>38.7</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
         <v>78</v>
@@ -4133,39 +4181,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4308,8 +4352,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4323,24 +4375,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -4348,31 +4400,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.9</v>
+        <v>34.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,65 +4438,61 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>16.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.6</v>
+        <v>38.7</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>5.1</v>
+        <v>15.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4461,12 +4509,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4476,12 +4524,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4491,101 +4539,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4624,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4648,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>29.8</v>
+        <v>32.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,7 +4718,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -4672,10 +4728,10 @@
         <v>33.4</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
@@ -4685,39 +4741,35 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4860,8 +4912,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4900,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4924,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.7</v>
+        <v>32.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,7 +4998,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -4948,10 +5008,10 @@
         <v>33.4</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>50</v>
@@ -4961,39 +5021,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5136,8 +5192,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5151,24 +5215,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -5176,31 +5240,31 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.8</v>
+        <v>31.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,62 +5278,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>5.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>17.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5289,12 +5349,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5304,12 +5364,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5319,101 +5379,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5452,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.7</v>
+        <v>31.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5500,10 +5568,10 @@
         <v>37.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -5513,39 +5581,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5688,8 +5752,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6054,12 +6126,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6078,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>55.7</v>
+        <v>57.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>38.7</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6358,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6330,12 +6406,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -6354,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52.7</v>
+        <v>55.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6454,10 @@
         <v>33.4</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6391,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6638,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6581,24 +6661,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -6606,31 +6686,31 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.9</v>
+        <v>51.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,62 +6724,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>48.9</v>
+        <v>50.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>28.9</v>
+        <v>63.3</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6719,12 +6795,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -6734,12 +6810,12 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -6749,101 +6825,109 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6857,24 +6941,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -6882,31 +6966,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.8</v>
+        <v>50.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,62 +7004,58 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>50.1</v>
+        <v>43.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>33.4</v>
+        <v>38.7</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>63.3</v>
+        <v>0</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6995,27 +7075,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -7025,101 +7105,109 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7133,24 +7221,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -7158,31 +7246,31 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>48.1</v>
+        <v>49.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,62 +7284,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.6</v>
+        <v>41</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.4</v>
+        <v>38.7</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>65.2</v>
+        <v>20.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7271,27 +7355,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -7301,101 +7385,109 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7409,24 +7501,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -7434,31 +7526,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.4</v>
+        <v>48.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,62 +7564,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>65.2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7547,27 +7635,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7577,101 +7665,109 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7685,24 +7781,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -7710,31 +7806,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>47.4</v>
+        <v>48.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,62 +7844,58 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>38.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7823,27 +7915,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -7853,101 +7945,109 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7986,12 +8086,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8010,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>47</v>
+        <v>48.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,7 +8124,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8034,10 +8134,10 @@
         <v>33.4</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
@@ -8047,39 +8147,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8222,8 +8318,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8262,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8286,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.2</v>
+        <v>46.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8414,10 @@
         <v>33.4</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -8323,39 +8427,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8498,8 +8598,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8513,24 +8621,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -8538,31 +8646,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.3</v>
+        <v>45.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,62 +8684,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>38.2</v>
+        <v>43.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>33.4</v>
+        <v>38.7</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>25.3</v>
+        <v>54.9</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8651,12 +8755,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -8666,12 +8770,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8681,101 +8785,109 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8814,12 +8926,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8838,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,7 +8964,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -8862,10 +8974,10 @@
         <v>38.7</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T12" t="n">
         <v>78</v>
@@ -8875,39 +8987,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9050,8 +9158,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9065,12 +9181,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9090,12 +9206,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9114,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.9</v>
+        <v>38.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,62 +9244,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>23.3</v>
+        <v>11.6</v>
       </c>
       <c r="Q13" t="n">
         <v>38.7</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9208,7 +9320,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -9218,7 +9330,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -9233,67 +9345,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -9326,8 +9438,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9366,12 +9486,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9390,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>34</v>
+        <v>34.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,7 +9524,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9414,10 +9534,10 @@
         <v>38.7</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
         <v>78</v>
@@ -9427,39 +9547,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9602,8 +9718,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9617,24 +9741,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -9642,31 +9766,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.9</v>
+        <v>34.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,65 +9804,61 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>16.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.6</v>
+        <v>38.7</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>5.1</v>
+        <v>15.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -9755,12 +9875,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9770,12 +9890,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9785,101 +9905,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9918,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -9942,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>29.8</v>
+        <v>32.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,7 +10084,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -9966,10 +10094,10 @@
         <v>33.4</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
@@ -9979,39 +10107,35 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10154,8 +10278,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10194,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10218,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.7</v>
+        <v>32.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,7 +10364,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -10242,10 +10374,10 @@
         <v>33.4</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>50</v>
@@ -10255,39 +10387,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -10430,8 +10558,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10445,24 +10581,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -10470,31 +10606,31 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.8</v>
+        <v>31.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,62 +10644,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>5.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>17.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10583,12 +10715,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10598,12 +10730,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10613,101 +10745,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10746,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.7</v>
+        <v>31.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -10794,10 +10934,10 @@
         <v>37.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -10807,39 +10947,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10982,8 +11118,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
